--- a/data/trans_orig/P6705-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6705-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29254</t>
+          <t>29499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53590</t>
+          <t>54916</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>14964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35192</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49890</t>
+          <t>50201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81577</t>
+          <t>82646</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>26965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50473</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19036</t>
+          <t>19628</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39314</t>
+          <t>39296</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51304</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82088</t>
+          <t>83524</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80805</t>
+          <t>79148</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116292</t>
+          <t>114892</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38622</t>
+          <t>36888</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65135</t>
+          <t>63005</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>127399</t>
+          <t>125253</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>170082</t>
+          <t>168176</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55591</t>
+          <t>55623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87632</t>
+          <t>85640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28569</t>
+          <t>28328</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53255</t>
+          <t>51339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91948</t>
+          <t>90429</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130236</t>
+          <t>129347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45469</t>
+          <t>45799</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72228</t>
+          <t>72589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41082</t>
+          <t>39666</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65742</t>
+          <t>65891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92553</t>
+          <t>91946</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>128529</t>
+          <t>131658</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>17619</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38034</t>
+          <t>38788</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25406</t>
+          <t>24189</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47097</t>
+          <t>46511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46771</t>
+          <t>46260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75902</t>
+          <t>78195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42596</t>
+          <t>43488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18688</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39185</t>
+          <t>39567</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44400</t>
+          <t>43622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75156</t>
+          <t>74301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67172</t>
+          <t>66638</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100902</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41528</t>
+          <t>39620</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>65272</t>
+          <t>64992</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115035</t>
+          <t>114468</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>155033</t>
+          <t>154536</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54903</t>
+          <t>53628</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85718</t>
+          <t>85207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20635</t>
+          <t>19516</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41466</t>
+          <t>40924</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81157</t>
+          <t>79770</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117850</t>
+          <t>116320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,4%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36960</t>
+          <t>37226</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64747</t>
+          <t>63250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57414</t>
+          <t>57078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91180</t>
+          <t>89399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62332</t>
+          <t>63133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93069</t>
+          <t>94912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18402</t>
+          <t>18398</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36453</t>
+          <t>36914</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87033</t>
+          <t>87026</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123432</t>
+          <t>122737</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>33707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58805</t>
+          <t>59260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25082</t>
+          <t>25506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49512</t>
+          <t>48603</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77582</t>
+          <t>79061</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59711</t>
+          <t>57921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88330</t>
+          <t>89111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43703</t>
+          <t>42783</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>87898</t>
+          <t>88097</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>123767</t>
+          <t>123700</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,6%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35044</t>
+          <t>34816</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>59465</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>22632</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47207</t>
+          <t>47538</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75756</t>
+          <t>76876</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>26218</t>
+          <t>25473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48146</t>
+          <t>49190</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31681</t>
+          <t>31215</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44170</t>
+          <t>46202</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>73569</t>
+          <t>74904</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73710</t>
+          <t>75831</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>109970</t>
+          <t>110132</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>53619</t>
+          <t>53814</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83087</t>
+          <t>83422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135455</t>
+          <t>138626</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180751</t>
+          <t>185518</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56878</t>
+          <t>56690</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>87805</t>
+          <t>90699</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40419</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67720</t>
+          <t>67770</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>103655</t>
+          <t>105578</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>145503</t>
+          <t>146543</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>100716</t>
+          <t>101751</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>139530</t>
+          <t>140217</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55687</t>
+          <t>54733</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84301</t>
+          <t>83873</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>165683</t>
+          <t>164162</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>213298</t>
+          <t>210453</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52231</t>
+          <t>52776</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>82603</t>
+          <t>84805</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46531</t>
+          <t>48074</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>76352</t>
+          <t>76015</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>108000</t>
+          <t>108707</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>149641</t>
+          <t>148525</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>55971</t>
+          <t>56592</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88812</t>
+          <t>87489</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>35225</t>
+          <t>35947</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60681</t>
+          <t>62585</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>98323</t>
+          <t>100309</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>138938</t>
+          <t>140485</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29173</t>
+          <t>29324</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51245</t>
+          <t>51916</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>44691</t>
+          <t>44241</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71113</t>
+          <t>71656</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>81261</t>
+          <t>81155</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>116392</t>
+          <t>115332</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21813</t>
+          <t>21685</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42321</t>
+          <t>42526</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19976</t>
+          <t>19392</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39313</t>
+          <t>39689</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46651</t>
+          <t>47247</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>74864</t>
+          <t>75583</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>23,07%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>28199</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50898</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27275</t>
+          <t>26501</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>50781</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61579</t>
+          <t>61745</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>92992</t>
+          <t>95827</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>34801</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17083</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36622</t>
+          <t>37802</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>64627</t>
+          <t>64548</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>26968</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17058</t>
+          <t>17426</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>37563</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32428</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>57814</t>
+          <t>56447</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>245727</t>
+          <t>248919</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>308436</t>
+          <t>311306</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>185104</t>
+          <t>185698</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>238914</t>
+          <t>237904</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>448265</t>
+          <t>446847</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>529472</t>
+          <t>530487</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>189520</t>
+          <t>190249</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>245821</t>
+          <t>244108</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>131715</t>
+          <t>134227</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>178807</t>
+          <t>182991</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>340094</t>
+          <t>338213</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>415117</t>
+          <t>408749</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>374773</t>
+          <t>375739</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>446883</t>
+          <t>448309</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>214590</t>
+          <t>215316</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>271387</t>
+          <t>273997</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>605221</t>
+          <t>609750</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>695710</t>
+          <t>696577</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>246243</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>311365</t>
+          <t>308205</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>147401</t>
+          <t>146992</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>196785</t>
+          <t>196152</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>409349</t>
+          <t>408388</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>492050</t>
+          <t>487252</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>208043</t>
+          <t>205416</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>263891</t>
+          <t>262380</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>147360</t>
+          <t>145996</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>195300</t>
+          <t>194583</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>365555</t>
+          <t>364326</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>442629</t>
+          <t>442163</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41374</t>
+          <t>43050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68688</t>
+          <t>70276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27557</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49549</t>
+          <t>50260</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74446</t>
+          <t>73496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110516</t>
+          <t>110460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>40349</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67622</t>
+          <t>67129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22953</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43590</t>
+          <t>42188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>67351</t>
+          <t>67093</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>100901</t>
+          <t>101926</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68936</t>
+          <t>69186</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99094</t>
+          <t>102249</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49011</t>
+          <t>48984</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75608</t>
+          <t>75182</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>124330</t>
+          <t>126348</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>168805</t>
+          <t>167263</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35825</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60967</t>
+          <t>60724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37232</t>
+          <t>36140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61116</t>
+          <t>61412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76786</t>
+          <t>78668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112805</t>
+          <t>113810</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30037</t>
+          <t>29638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56196</t>
+          <t>55724</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24840</t>
+          <t>25805</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47093</t>
+          <t>46793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60800</t>
+          <t>61432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95114</t>
+          <t>94148</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45086</t>
+          <t>44001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72150</t>
+          <t>73080</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35178</t>
+          <t>35281</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58434</t>
+          <t>59616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87255</t>
+          <t>86833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123366</t>
+          <t>123854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37765</t>
+          <t>37528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>65982</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31536</t>
+          <t>32691</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52889</t>
+          <t>54276</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74557</t>
+          <t>74875</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109375</t>
+          <t>111440</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50564</t>
+          <t>48431</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77879</t>
+          <t>78872</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41620</t>
+          <t>41734</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>66121</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>98734</t>
+          <t>99035</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137464</t>
+          <t>135793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31774</t>
+          <t>31492</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56288</t>
+          <t>55358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19144</t>
+          <t>19811</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39997</t>
+          <t>39750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55974</t>
+          <t>56911</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>87647</t>
+          <t>87875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>21415</t>
+          <t>20409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42082</t>
+          <t>42691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29142</t>
+          <t>27928</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36863</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63811</t>
+          <t>64291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40645</t>
+          <t>41117</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66687</t>
+          <t>67921</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32054</t>
+          <t>31517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62529</t>
+          <t>63224</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93669</t>
+          <t>91097</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33236</t>
+          <t>33731</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56399</t>
+          <t>57401</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10348</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23908</t>
+          <t>23378</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47539</t>
+          <t>45835</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75206</t>
+          <t>74784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>54996</t>
+          <t>54484</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81899</t>
+          <t>81764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>19756</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64449</t>
+          <t>64919</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>96595</t>
+          <t>95950</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28407</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50953</t>
+          <t>50717</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>17321</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36550</t>
+          <t>36548</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61898</t>
+          <t>62711</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22939</t>
+          <t>22878</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12768</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>30193</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107145</t>
+          <t>107581</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>146345</t>
+          <t>150415</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48800</t>
+          <t>49573</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76852</t>
+          <t>77166</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>163859</t>
+          <t>166377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>214381</t>
+          <t>213436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>75323</t>
+          <t>75143</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>109265</t>
+          <t>109253</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>56012</t>
+          <t>55524</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83525</t>
+          <t>86526</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>140047</t>
+          <t>139576</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>186758</t>
+          <t>187579</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>116843</t>
+          <t>115821</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>156352</t>
+          <t>155089</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>90849</t>
+          <t>89971</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>125637</t>
+          <t>125290</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>217983</t>
+          <t>215701</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>269928</t>
+          <t>269492</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>69434</t>
+          <t>71018</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>105793</t>
+          <t>104855</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56395</t>
+          <t>55423</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86349</t>
+          <t>86114</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>135820</t>
+          <t>136651</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>182018</t>
+          <t>181303</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37493</t>
+          <t>36266</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>64285</t>
+          <t>63792</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>45665</t>
+          <t>44380</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>73281</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89606</t>
+          <t>87902</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>129665</t>
+          <t>126514</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>52857</t>
+          <t>54015</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80747</t>
+          <t>80884</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50457</t>
+          <t>50184</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76770</t>
+          <t>77227</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>111248</t>
+          <t>112162</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>148959</t>
+          <t>149723</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24549</t>
+          <t>24151</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46214</t>
+          <t>46483</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34850</t>
+          <t>35845</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>58454</t>
+          <t>58810</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>65700</t>
+          <t>64952</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>97591</t>
+          <t>96730</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43519</t>
+          <t>43747</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>69428</t>
+          <t>69063</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8046,12 +8046,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38062</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61891</t>
+          <t>61748</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8081,12 +8081,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>89512</t>
+          <t>86461</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>123957</t>
+          <t>122809</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +8124,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17293</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37010</t>
+          <t>36462</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16334</t>
+          <t>15761</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>34387</t>
+          <t>34225</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8194,12 +8194,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>37335</t>
+          <t>37506</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>64272</t>
+          <t>63412</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +8237,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>21405</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8252,12 +8252,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8272,12 +8272,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>24737</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8307,12 +8307,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>16510</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>39529</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>326370</t>
+          <t>324492</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>393856</t>
+          <t>392037</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>206155</t>
+          <t>205134</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>260404</t>
+          <t>260319</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>543645</t>
+          <t>551474</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>635572</t>
+          <t>631554</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +8580,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>241052</t>
+          <t>237920</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>300361</t>
+          <t>303326</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8595,12 +8595,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8615,12 +8615,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>176482</t>
+          <t>178525</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>230072</t>
+          <t>228779</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>438279</t>
+          <t>434023</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>517907</t>
+          <t>517606</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8665,12 +8665,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8693,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>375344</t>
+          <t>371930</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>443476</t>
+          <t>440804</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8728,12 +8728,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>255296</t>
+          <t>255488</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>314775</t>
+          <t>314477</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8743,12 +8743,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>644017</t>
+          <t>645264</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>736390</t>
+          <t>735593</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8778,12 +8778,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8806,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>211360</t>
+          <t>214534</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>268993</t>
+          <t>274768</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8841,12 +8841,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>158366</t>
+          <t>158214</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>207959</t>
+          <t>209075</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8856,12 +8856,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>387824</t>
+          <t>384746</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>463919</t>
+          <t>460966</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8919,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>124050</t>
+          <t>123116</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>172209</t>
+          <t>171747</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>112571</t>
+          <t>113520</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>155723</t>
+          <t>156956</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8969,12 +8969,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>245730</t>
+          <t>247474</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>316337</t>
+          <t>311185</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9004,12 +9004,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -9377,32 +9377,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28617</t>
+          <t>30465</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19815</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39834</t>
+          <t>43649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9412,32 +9412,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>20775</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34221</t>
+          <t>36621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9447,32 +9447,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54551</t>
+          <t>58943</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42304</t>
+          <t>45622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67509</t>
+          <t>73307</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -9490,69 +9490,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26885</t>
+          <t>30326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>20,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30,32%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>11175</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5996</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17959</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>20,67%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10770</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6060</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17762</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>13,16%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>21,71%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>32</t>
@@ -9560,32 +9560,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>29169</t>
+          <t>31323</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20410</t>
+          <t>22523</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39868</t>
+          <t>42956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -9603,32 +9603,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>26458</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>17071</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30400</t>
+          <t>37748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9638,32 +9638,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19635</t>
+          <t>19970</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>28312</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9673,32 +9673,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>40438</t>
+          <t>46428</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30503</t>
+          <t>34526</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52566</t>
+          <t>58602</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -9716,32 +9716,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16526</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9751,32 +9751,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15858</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9786,32 +9786,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>25465</t>
+          <t>27713</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35755</t>
+          <t>38175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -9829,32 +9829,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>22498</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9864,32 +9864,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>9726</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9899,32 +9899,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>22495</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13285</t>
+          <t>14699</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31446</t>
+          <t>33582</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -9942,17 +9942,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88998</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9977,17 +9977,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81831</t>
+          <t>86895</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10012,17 +10012,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>186902</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10059,32 +10059,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21835</t>
+          <t>24151</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30772</t>
+          <t>33534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10094,32 +10094,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>24900</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>17225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28984</t>
+          <t>32335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10129,32 +10129,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43527</t>
+          <t>49050</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32946</t>
+          <t>37308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55436</t>
+          <t>60125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -10172,32 +10172,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19501</t>
+          <t>20516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10207,32 +10207,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10366</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16620</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10242,32 +10242,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>21053</t>
+          <t>22618</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>31722</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -10285,32 +10285,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22552</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14771</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31419</t>
+          <t>32894</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10320,32 +10320,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19472</t>
+          <t>20404</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13703</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10355,32 +10355,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>42024</t>
+          <t>43065</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>32661</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53330</t>
+          <t>53793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>37,98%</t>
         </is>
       </c>
     </row>
@@ -10398,32 +10398,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>13441</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10433,32 +10433,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10468,32 +10468,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>10428</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -10511,32 +10511,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8548</t>
+          <t>9058</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10546,17 +10546,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3387</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12230</t>
+          <t>12672</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10581,32 +10581,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8950</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25411</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -10624,17 +10624,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>74377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10659,17 +10659,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62011</t>
+          <t>67273</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10694,17 +10694,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>131126</t>
+          <t>141650</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10741,32 +10741,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>262532</t>
+          <t>19585</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71873</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>299969</t>
+          <t>28986</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10776,32 +10776,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>9344</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10811,32 +10811,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>271083</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87953</t>
+          <t>19633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320773</t>
+          <t>39885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -10854,32 +10854,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14447</t>
+          <t>16289</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81116</t>
+          <t>26515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10889,32 +10889,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6346</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10924,32 +10924,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>17071</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71141</t>
+          <t>30653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -10967,32 +10967,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>20793</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>109941</t>
+          <t>30735</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11002,32 +11002,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>8081</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>27341</t>
+          <t>28874</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>110919</t>
+          <t>39018</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -11080,32 +11080,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25335</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11115,32 +11115,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11150,32 +11150,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>10051</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40576</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -11193,32 +11193,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54474</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11228,32 +11228,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>795</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11263,32 +11263,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>11018</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49397</t>
+          <t>25735</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -11306,17 +11306,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>310094</t>
+          <t>70757</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11341,17 +11341,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>28928</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11376,17 +11376,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>335722</t>
+          <t>99685</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11423,32 +11423,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>32878</t>
+          <t>35001</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>24752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45048</t>
+          <t>47186</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11458,32 +11458,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24891</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17555</t>
+          <t>20847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>37348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11493,32 +11493,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>57769</t>
+          <t>63516</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46608</t>
+          <t>49793</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71338</t>
+          <t>77973</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -11536,32 +11536,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>21478</t>
+          <t>22597</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>14653</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31780</t>
+          <t>35012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11571,32 +11571,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>20702</t>
+          <t>23996</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29280</t>
+          <t>32986</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11606,32 +11606,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>42180</t>
+          <t>46593</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31255</t>
+          <t>33996</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56227</t>
+          <t>59786</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -11649,32 +11649,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>37502</t>
+          <t>40724</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>29242</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50013</t>
+          <t>53312</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11684,32 +11684,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>38027</t>
+          <t>41374</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29992</t>
+          <t>32460</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>46711</t>
+          <t>51378</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11719,32 +11719,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>75529</t>
+          <t>82098</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>61663</t>
+          <t>67299</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>90033</t>
+          <t>98082</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -11762,32 +11762,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>26203</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>18641</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37132</t>
+          <t>41844</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11797,32 +11797,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12628</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>20317</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11832,32 +11832,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>38831</t>
+          <t>42630</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28331</t>
+          <t>32305</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51369</t>
+          <t>56101</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,2%</t>
         </is>
       </c>
     </row>
@@ -11875,32 +11875,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>7526</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11910,32 +11910,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>10380</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5565</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16480</t>
+          <t>17066</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11945,32 +11945,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15665</t>
+          <t>17906</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23701</t>
+          <t>27823</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -11988,17 +11988,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12023,17 +12023,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>106232</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>106232</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106232</t>
+          <t>118281</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12058,17 +12058,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>229973</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>229973</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>229973</t>
+          <t>252743</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12105,32 +12105,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>25923</t>
+          <t>33967</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>22540</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37682</t>
+          <t>47128</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12140,32 +12140,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>25451</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18440</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32669</t>
+          <t>39186</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12175,32 +12175,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>51374</t>
+          <t>64136</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>40225</t>
+          <t>50360</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>66723</t>
+          <t>80117</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -12218,32 +12218,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>21479</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9517</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28666</t>
+          <t>35237</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12253,32 +12253,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17440</t>
+          <t>21016</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12288,32 +12288,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>28631</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19442</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>49539</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -12331,32 +12331,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15679</t>
+          <t>22331</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24336</t>
+          <t>33307</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12366,32 +12366,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23762</t>
+          <t>27480</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31183</t>
+          <t>36038</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12401,32 +12401,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>39442</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>30116</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>50314</t>
+          <t>62636</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -12444,32 +12444,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -12479,32 +12479,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>22186</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -12514,32 +12514,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>20970</t>
+          <t>26677</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>31422</t>
+          <t>40068</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -12557,32 +12557,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>8997</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12592,32 +12592,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12627,32 +12627,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>13514</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -12670,17 +12670,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>94264</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12705,17 +12705,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>88235</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12740,17 +12740,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12787,32 +12787,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>371784</t>
+          <t>143169</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>190133</t>
+          <t>122598</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>545159</t>
+          <t>168851</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12822,32 +12822,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>106521</t>
+          <t>121405</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>90396</t>
+          <t>106208</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>121982</t>
+          <t>140577</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12857,32 +12857,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>478304</t>
+          <t>264574</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>298737</t>
+          <t>237997</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>753972</t>
+          <t>294851</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -12900,32 +12900,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>82417</t>
+          <t>92765</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>32167</t>
+          <t>73919</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>139436</t>
+          <t>115717</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12935,32 +12935,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>55687</t>
+          <t>62502</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>44759</t>
+          <t>49930</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>68351</t>
+          <t>77126</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12970,32 +12970,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>138104</t>
+          <t>155267</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>71804</t>
+          <t>134485</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>191851</t>
+          <t>181663</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -13013,32 +13013,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>116841</t>
+          <t>132966</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>40175</t>
+          <t>111376</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>195717</t>
+          <t>156949</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13048,32 +13048,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>107933</t>
+          <t>117309</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>94782</t>
+          <t>101469</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>126417</t>
+          <t>133300</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13083,32 +13083,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>224774</t>
+          <t>250275</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>109608</t>
+          <t>223271</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>302363</t>
+          <t>278734</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -13126,32 +13126,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>55688</t>
+          <t>62531</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>48096</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>94577</t>
+          <t>81167</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13161,32 +13161,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>47909</t>
+          <t>54969</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>37691</t>
+          <t>42507</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>59818</t>
+          <t>67933</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13196,32 +13196,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>103597</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>49605</t>
+          <t>99259</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>146050</t>
+          <t>138060</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -13239,32 +13239,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>37597</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>66193</t>
+          <t>60150</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13274,32 +13274,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>31538</t>
+          <t>33427</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22792</t>
+          <t>24357</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>42635</t>
+          <t>43266</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13309,32 +13309,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>69135</t>
+          <t>75865</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>29139</t>
+          <t>58859</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>100490</t>
+          <t>94677</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
+          <t>8,79%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
           <t>6,82%</t>
         </is>
       </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -13352,17 +13352,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>664326</t>
+          <t>473868</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -13387,17 +13387,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>349588</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>349588</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>349588</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -13422,17 +13422,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1013914</t>
+          <t>863480</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1013914</t>
+          <t>863480</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1013914</t>
+          <t>863480</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
